--- a/output/pdf_financials_xlsx/HPSS.xlsx
+++ b/output/pdf_financials_xlsx/HPSS.xlsx
@@ -1898,13 +1898,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.242167</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.762274</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.744516</v>
       </c>
     </row>
     <row r="93">
@@ -3304,7 +3304,11 @@
           <t>Reserves 18</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -3585,7 +3589,11 @@
           <t>Share-based payment reserve 18</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" s="5" t="n">
         <v>0.242167</v>
       </c>

--- a/output/pdf_financials_xlsx/HPSS.xlsx
+++ b/output/pdf_financials_xlsx/HPSS.xlsx
@@ -964,13 +964,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.002888</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.342071</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.062997</v>
       </c>
     </row>
     <row r="35">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.002888</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.342071</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.062997</v>
       </c>
     </row>
     <row r="37">
@@ -1188,13 +1188,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.152032</v>
+        <v>0.149144</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.665597</v>
+        <v>0.323526</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.150611</v>
+        <v>0.087614</v>
       </c>
     </row>
     <row r="49">
@@ -2401,13 +2401,13 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.056728</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.058476</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.051745</v>
       </c>
     </row>
     <row r="125">
@@ -2417,13 +2417,13 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.056728</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.058476</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.051745</v>
       </c>
     </row>
     <row r="126">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -4559,7 +4559,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
@@ -5099,7 +5103,11 @@
           <t>Lease payments 9</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E82" s="5" t="n">
         <v>-0.056728</v>
       </c>

--- a/output/pdf_financials_xlsx/HPSS.xlsx
+++ b/output/pdf_financials_xlsx/HPSS.xlsx
@@ -2215,7 +2215,7 @@
         <v>0</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.004234</v>
       </c>
     </row>
     <row r="113">
@@ -4321,7 +4321,11 @@
           <t>Proceeds from sale of property and equipment</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/HPSS.xlsx
+++ b/output/pdf_financials_xlsx/HPSS.xlsx
@@ -1498,13 +1498,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.174567</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.266587</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.438288</v>
       </c>
     </row>
     <row r="68">
@@ -3810,7 +3810,11 @@
           <t>Deferred income tax recovery 21</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E39" s="5" t="n">
         <v>-0.056118</v>
       </c>
